--- a/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A 28-year-old man with severe aortic valve stenosis is scheduled for aortic valve replacement via ministernotomy. The procedure is performed with an incision:</t>
+          <t>A 28-year-old man with severe aortic valve stenosis is scheduled for aortic valve replacement via ministernotomy. The procedure is performed with an incision</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pneumothorax is generally NOT associated with:</t>
+          <t>Pneumothorax is generally NOT associated with</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glaucoma is:</t>
+          <t>Glaucoma is</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>An eight-year-old patient is brought to the Emergency Department because of the onset of a painful, erythematous anterior midline cervical swelling. During swallowing, a relationship with the hyoid bone is noted. Which of the following is the most likely diagnosis?</t>
+          <t>An eight-year-old patient is brought to the Emergency Department for the onset of a painful, erythematous anterior midline cervical swelling. On swallowing, movement in relation to the hyoid bone is appreciated. Which of the following is the most likely diagnosis?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A 55-year-old patient, who underwent implant surgery two years earlier at the level of the right upper alveolar arch, complains of facial pain in the right infraorbital region for several days. Endoscopic examination shows edema and purulent secretions affecting the right ostiomeatal complex. Which of the following is the most likely diagnosis?</t>
+          <t>A 55-year-old patient, who underwent implant surgery two years earlier at the level of the right maxillary alveolar arch, complains of pain for several days in the right infraorbital facial region. Endoscopic examination reveals edema and purulent secretions involving the right ostiomeatal complex. Which of the following is the most likely diagnosis?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A 39-year-old patient presents to the Emergency Department with left anterior chest pain that worsens with respiratory movements. On clinical evaluation, tachypnea is noted with a respiratory rate of 34 breaths/minute. Physical examination reveals reduced vesicular breath sounds on the left. Arterial blood gas (on room air): pH 7.50, PaO2 62 mmHg, PaCO2 28 mmHg. A chest X-ray is performed, and the radiograph is attached. The clinical, radiological, and blood gas findings are most consistent with:</t>
+          <t>A 39-year-old patient presents to the Emergency Department with left anterior chest pain that worsens with respiratory movements. On clinical evaluation, tachypnea is noted with a respiratory rate of 34 breaths/minute. Physical examination reveals decreased vesicular breath sounds on the left. Arterial blood gas (on room air): pH 7.50, PaO2 62 mmHg, PaCO2 28 mmHg. A chest X-ray is performed, and the radiograph is attached. The clinical, radiological, and blood gas findings are most consistent with:</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Extensive left bronchopneumonic infiltrate warranting antibiotic therapy</t>
+          <t>Extensive left bronchopneumonic focus warranting antibiotic therapy</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>In a newborn, type III esophageal atresia is:</t>
+          <t>In a newborn, type III esophageal atresia is</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A 35-year-old woman presents to the gynecology clinic reporting amenorrhea for approximately 6 months, sleep disturbances, and dyspareunia. In previous years, her menstrual cycles had always been regular in terms of frequency, duration, and flow. She brings hormonal tests showing elevated FSH and LH levels, low Estradiol and Progesterone levels, and nothing else of relevance. The most likely cause of amenorrhea is:</t>
+          <t>A 35-year-old woman presents to the gynecology clinic reporting amenorrhea for approximately 6 months, sleep disturbances, and dyspareunia. In previous years, her menstrual cycles had always been regular in terms of frequency, duration, and flow. She brings hormonal tests showing elevated FSH and LH levels, low Estradiol and Progesterone levels, and nothing else of relevance. The most likely cause of amenorrhea is</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A 45-year-old pregnant woman at the seventeenth week of gestation, with a combined first-trimester screening test (bitest) showing high risk due to increased nuchal translucency, undergoes amniocentesis. The fetal karyotype result reveals trisomy 13, which causes the following syndrome:</t>
+          <t>A 45-year-old pregnant woman at the seventeenth week of gestation, with a combined first-trimester screening test (bitest) showing high risk due to increased nuchal translucency, undergoes amniocentesis. The fetal karyotype result reveals trisomy 13, which causes the following syndrome</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A 60-year-old woman, postmenopausal for 5 years, presents to the gynecology outpatient clinic reporting vaginal bleeding for the past few days. The woman reports to the physician that she recently underwent a Pap test with a normal result and that she has had no genital trauma or sexual intercourse in the past few days. The most appropriate initial diagnostic strategy among the following is:</t>
+          <t>A 60-year-old woman, postmenopausal for 5 years, presents to the gynecology outpatient clinic reporting vaginal bleeding for the past few days. The woman reports to the physician that she recently underwent a Pap test with a normal result and that she has had no genital trauma or sexual intercourse in the past few days. The most appropriate initial diagnostic strategy among the following is</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A pregnant woman at the thirty-fourth week of gestation presents to the Emergency Department with severe pelvic pain, intense headache, and band-like abdominal pain. The clinical picture reveals BP = 150/100, tetanic uterine contractions, genital bleeding, cervical dilatation of 2 cm, and cardiotocographic tracing abnormalities with bradycardia and late decelerations. The most likely diagnosis is:</t>
+          <t>A pregnant woman at the thirty-fourth week of gestation presents to the Emergency Department with severe pelvic pain, intense headache, and band-like abdominal pain. The clinical picture reveals BP = 150/100, tetanic uterine contractions, genital bleeding, cervical dilatation of 2 cm, and cardiotocographic tracing abnormalities with bradycardia and late decelerations. The most likely diagnosis is</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A 53-year-old woman who works as a secretary reports to her physician symptoms in her right hand that began several months ago. Specifically, she complains of pain and paresthesias in the first three fingers of the hand that worsen at night. The pain and paresthesias worsen with hyperflexion of the wrist, and Tinel's sign is positive. On inspection, hypotrophy of the thenar eminence on the affected side is noted. Which of the following is the most likely diagnosis?</t>
+          <t>A 53-year-old woman who works as a secretary reports to her physician symptoms in her right hand that began several months ago. Specifically, she complains of pain and paresthesias in the first three fingers of the hand that worsen at night. The pain and paresthesias worsen with hyperflexion of the wrist, and Tinel's sign is positive. On inspection, atrophy of the thenar eminence on the affected side is noted. Which of the following is the most likely diagnosis?</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A 70-year-old man presents to the urologist for a total PSA value of 20.6 ng/mL. On physical examination, the digital rectal examination is equivocal for prostate cancer. The diagnostic workup currently considered most appropriate among the following is:</t>
+          <t>A 70-year-old man presents to the urologist for a total PSA value of 20.6 ng/mL. On physical examination, the digital rectal examination is equivocal for prostate cancer. The diagnostic workup currently considered most appropriate among the following is</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A 65-year-old patient, who underwent radical prostatectomy 3 months ago for a neoplasm with a Gleason score of 3+3, reports daytime and nighttime incontinence. The most likely diagnosis among the following is:</t>
+          <t>A 65-year-old patient, who underwent radical prostatectomy 3 months ago for a neoplasm with a Gleason score of 3+3, reports daytime and nighttime incontinence. The most likely diagnosis among the following is</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Assess respiratory and circulatory stability, establish venous access, perform blood tests</t>
+          <t>Assess respiratory and circulatory stability, establish venous access, and perform blood tests (measurement of serum salicylate level, arterial blood gas analysis, blood glucose, serum electrolytes, serum creatinine, and urinalysis).</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A 60-year-old female patient presents to the dermatology department with a diffuse morbilliform maculopapular eruption, facial edema, intense pruritus, and high fever. Three weeks earlier she had started treatment with allopurinol. Blood tests are performed, revealing hypereosinophilia (2000/mm3), atypical lymphocytes (more than 5%), and elevated transaminases, lipase, and amylase. The clinical picture is consistent with:</t>
+          <t>A 60-year-old female patient presents to the dermatology department with a diffuse morbilliform maculopapular eruption, facial edema, intense pruritus, and high fever. Three weeks earlier she had started treatment with allopurinol. Blood tests are performed, revealing hypereosinophilia (2000/mm3), atypical lymphocytes (more than 5%), and elevated transaminases, lipase, and amylase. The clinical picture is consistent with</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>On the peripheral blood smear, this erythrocyte morphology with schistocytes is observed. The picture is indicative of:</t>
+          <t>On the peripheral blood smear, this erythrocyte morphology with schistocytes is observed. The picture is indicative of</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A 40-year-old female patient with hypertension and a recent diagnosis of papillary thyroid carcinoma has undergone total thyroidectomy and subsequent radioiodine therapy. In light of this information, the trend of which of the following parameters should be monitored during this patient's follow-up:</t>
+          <t>A 40-year-old female patient with hypertension and a recent diagnosis of papillary thyroid carcinoma has undergone total thyroidectomy and subsequent radioiodine therapy. In light of this information, the trend of which of the following parameters should be monitored during this patient's follow-up</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>A 77-year-old man, with progressive deterioration of his general condition, presents on neurological examination with resting tremor, hypertonia, muscular rigidity, and micrographia. The most likely diagnostic hypothesis among the following is:</t>
+          <t>A 77-year-old man, with progressive deterioration of his general condition, presents on neurological examination with resting tremor, hypertonia, muscular rigidity, and micrographia. The most likely diagnostic hypothesis among the following is</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>The first-line drug, in the absence of contraindications, in a 54-year-old female patient diagnosed with stable angina detected during a visit to the cardiology outpatient clinic is:</t>
+          <t>The first-line drug, in the absence of contraindications, in a 54-year-old female patient diagnosed with stable angina detected during a visit to the cardiology outpatient clinic is</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>A 50-year-old man has been diagnosed with idiopathic dilated cardiomyopathy. Therapy with ACE inhibitors and beta-blockers has been prescribed. In this case, it would also be necessary to prescribe therapy with:</t>
+          <t>A 50-year-old man has been diagnosed with idiopathic dilated cardiomyopathy. Therapy with ACE inhibitors and beta-blockers has been prescribed. In this case, it would also be necessary to prescribe therapy with</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>A 77-year-old woman is being evaluated for possible pacemaker implantation. A definite indication for pacemaker implantation in the case of atrioventricular (A-V) block is given by:</t>
+          <t>A 77-year-old woman is being evaluated for possible pacemaker implantation. A definite indication for pacemaker implantation in the case of atrioventricular (A-V) block is given by</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>A 63-year-old patient with dysmetabolic and alcohol-related liver cirrhosis was recently discharged from the gastroenterology ward where he had been admitted for a confusional state secondary to hepatic encephalopathy. Which of the following therapies is most appropriate for the prevention of recurrent hepatic encephalopathy?</t>
+          <t>A 63-year-old patient with dysmetabolic and alcohol-related liver cirrhosis was recently discharged from the gastroenterology ward, where he had been admitted for a confusional state secondary to hepatic encephalopathy. Which of the following therapies is most appropriate for the prevention of recurrent hepatic encephalopathy?</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>A 65-year-old woman, a former smoker with a 40 pack-year history, who has COPD with an FEV1 equal to 28% of predicted (last spirometry performed approximately six months ago) presents for evaluation with the following arterial blood gas analysis performed while the patient was breathing room air: pH=7.35, PaO2=40 mmHg, PaCO2=55 mmHg, HCO3-=27 mmol/L. This blood gas analysis is most indicative of a patient with:</t>
+          <t>A 65-year-old woman, a former smoker with a 40 pack-year history, who has COPD with an FEV1 equal to 28% of predicted (last spirometry performed approximately six months ago) presents for evaluation with the following arterial blood gas analysis performed while the patient was breathing room air: pH=7.35, PaO2=40 mmHg, PaCO2=55 mmHg, HCO3-=27 mmol/L. This blood gas analysis is most indicative of a patient with</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Pure respiratory alkalosis</t>
+          <t>Respiratory alkalosis</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>A 75-year-old man with known ischemic heart disease is brought to the Emergency Department for the onset during the night of progressively worsening dyspnea. On arrival, the patient is alert and tachypneic. Chest auscultation reveals bilateral moist crackles with a "rising tide" pattern. Blood pressure is 185/90 mmHg, heart rate is 130 bpm, with a PaO2 of 45 mmHg on room air and a pH of 7.33. Which of the following is the first intervention to be undertaken?</t>
+          <t>A 75-year-old man with known ischemic heart disease is brought to the Emergency Department for the onset during the night of progressively worsening dyspnea. On arrival, the patient is alert and tachypneic. Chest auscultation reveals bilateral moist "rising tide" crackles. Blood pressure is 185/90 mmHg, heart rate is 130 bpm, with a PaO2 of 45 mmHg on room air and a pH of 7.33. Which of the following is the first intervention to be undertaken?</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Placement of rotating tourniquets on four limbs</t>
+          <t>Placement of rotating tourniquets on all four limbs</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A 30-year-old man is found in a public garden by emergency medical services personnel, unconscious, bradypneic, and with a pulse present. Signs of recent venipuncture are evident, and a tourniquet is present. The pupils are miotic, and blood pressure is 90/60 mmHg. The drug to be administered among the following is:</t>
+          <t>A 30-year-old man is found in a public garden by emergency medical services personnel, unconscious, bradypneic, and with a pulse present. Signs of recent venipuncture are evident, and a tourniquet is present. The pupils are miotic, and blood pressure is 90/60 mmHg. The drug to be administered among the following is</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>An 80-year-old man has had fever and otalgia for several days, for which he has used a topical antibiotic. Due to the persistence of symptoms, the patient goes to the Emergency Department. Laboratory tests reveal neutrophilic leukocytosis and an increase in C-reactive protein. During observation in the ED, the patient develops a fever spike with nuchal rigidity and subsequent reduction in level of consciousness progressing to coma. Among the following, the most likely hypothesis is that the patient has developed:</t>
+          <t>An 80-year-old man has had fever and otalgia for several days, for which he has used a topical antibiotic. Due to the persistence of symptoms, the patient goes to the Emergency Department. Laboratory tests reveal neutrophilic leukocytosis and an increase in C-reactive protein. During observation in the ED, the patient develops a fever spike with nuchal rigidity and subsequent reduction in level of consciousness progressing to coma. Among the following, the most likely hypothesis is that the patient has developed</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CHA2DS2-VASc</t>
+          <t>CHA₂DS₂-VASc</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>The current staging of chronic kidney disease according to international and national guidelines:</t>
+          <t>The current staging of chronic kidney disease according to international and national guidelines</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>A 60-year-old woman with type 1 diabetes mellitus since the age of 28, complicated by diabetic retinopathy and nephropathy, has an LDL cholesterol of 130 mg/dL in the absence of lipid-lowering therapy. According to the 2019 ESC guidelines, her target should be:</t>
+          <t>A 60-year-old woman with type 1 diabetes mellitus since the age of 28, complicated by diabetic retinopathy and nephropathy, has an LDL cholesterol of 130 mg/dL in the absence of lipid-lowering therapy. According to the 2019 ESC guidelines, her target should be</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>An 80-year-old patient presents to the Emergency Department for the acute onset, approximately two hours earlier, of weakness of the right hemibody. Neurological examination: the patient is alert and cooperative; motor deficit of the right limbs with early drift on the Mingazzini maneuver, mild language deficit with anomia. The diagnostic investigation to be performed immediately is:</t>
+          <t>An 80-year-old patient presents to the Emergency Department for the acute onset, approximately two hours earlier, of weakness of the right hemibody. Neurological examination: the patient is alert and cooperative; motor deficit of the right limbs with early drift on the Mingazzini maneuver, mild language deficit with anomia. The diagnostic investigation to be performed immediately is</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Gender dysphoria can be defined as:</t>
+          <t>Gender dysphoria can be defined as</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Myocardial scintigraphy is indicated for studying:</t>
+          <t>Myocardial scintigraphy is indicated for studying</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>68Ga-DOTA-peptides (DOTATATE, DOTATOC, DOTANOC) are PET radiopharmaceuticals routinely used for the study of:</t>
+          <t>68Ga-DOTA-peptides (DOTATATE, DOTATOC, DOTANOC) are PET radiopharmaceuticals routinely used for the study of</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>A 23-year-old woman has had a nodule in the upper inner quadrant of the left breast for approximately two months which, she reports, has been growing. When the patient presents to her physician, the nodule is 2.2 cm, clinically has well-defined margins, is mobile, and has a firm-elastic consistency. An ultrasound-guided biopsy is performed, and histological examination shows: "Fibroepithelial lesion with diffusely increased stromal cellularity in the absence of atypia; glandular proliferation with features of ductal hyperplasia without atypia. There is 1 mitosis/10 HPF." Based on the clinical and histological findings, which of the following is the most likely diagnosis?</t>
+          <t>A 23-year-old woman has had a nodule in the upper inner quadrant of the left breast for approximately two months which, she reports, has been enlarging. When the patient presents to her physician, the nodule is 2.2 cm, clinically has well-defined margins, is mobile, and has a firm-elastic consistency. An ultrasound-guided biopsy is performed, and histological examination shows: "Fibroepithelial lesion with diffusely increased stromal cellularity in the absence of atypia; glandular proliferation with features of ductal hyperplasia without atypia. There is 1 mitosis/10 HPF." Based on the clinical and histological findings, which of the following is the most likely diagnosis?</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>A 54-year-old woman, during routine blood tests, shows an increase in TSH with normal fT3 and fT4 values. A thyroid ultrasound is performed, which shows the presence of multiple nodules, including a nodule in the left lobe, with a maximum diameter of 18 mm, hypoechoic in appearance, with irregular borders and the presence of microcalcifications. Fine-needle aspiration of this nodule is performed, and cytological examination shows: "Numerous red blood cells associated with groups of cells with enlarged, oval nuclei, sometimes overlapping, showing nuclear grooves and pseudoinclusions." Based on the clinical and cytological findings, which of the following is the most likely diagnosis?</t>
+          <t>A 54-year-old woman, during routine blood tests, shows an elevated TSH with normal fT3 and fT4 values. A thyroid ultrasound is performed, which reveals the presence of multiple nodules, including a nodule in the left lobe, with a maximum diameter of 18 mm, hypoechoic in appearance, with irregular borders and the presence of microcalcifications. Fine-needle aspiration of this nodule is performed, and cytological examination shows: "Numerous erythrocytes associated with groups of cells with enlarged, oval nuclei, occasionally overlapping, showing nuclear grooves and pseudoinclusions." Based on the clinical and cytological findings, which of the following is the most likely diagnosis?</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Use mosquito repellents</t>
+          <t>Use repellents to avoid mosquito bites</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>A gastroscopy and a rectocolonoscopy are prescribed for suspected internal bleeding due to chronic blood loss</t>
+          <t>A gastroscopy and colonoscopy are prescribed for suspected anemia due to chronic blood loss.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>The diagnosis of phenylketonuria is usually made in the context of:</t>
+          <t>The diagnosis of phenylketonuria is usually made in the context of</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Neonatal diagnostic approaches carried out selectively on children of patients affected by this or other amino acid metabolism disorders</t>
+          <t>Neonatal diagnostic approaches performed selectively on offspring of patients affected by this or other amino acid metabolism disorders</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>The measles vaccine is:</t>
+          <t>The measles vaccine is</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tetanus toxin:</t>
+          <t>Tetanus toxin</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Among epidemiological studies:</t>
+          <t>Among epidemiological studies</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>A 3-year-old child is brought for medical evaluation accompanied by the parents, who report an accidental fall down the stairs. The child appears frightened and, on inspection, the healthcare providers note the presence of multiple ecchymoses at different stages of coloration on the dorsal region of both forearms. Radiological examinations show evidence of fractures, including "greenstick" fractures, of the limbs. The healthcare providers consult one another regarding the need to inform the judicial authority. This obligation falls upon:</t>
+          <t>A 3-year-old child is brought for medical evaluation accompanied by the parents, who report an accidental fall down the stairs. The child appears frightened and, on inspection, the healthcare providers note the presence of multiple ecchymoses at different stages of coloration on the dorsal region of both forearms. Radiological examinations show evidence of fractures, including "greenstick" fractures, of the limbs. The healthcare providers consult one another regarding the need to inform the judicial authority. This obligation falls upon</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>For a group of 500 patients, a relative risk (RR) of 5.65 was calculated with respect to exposure to a specific risk factor. This means that the probability of developing a certain disease is:</t>
+          <t>For a group of 500 patients, a relative risk (RR) of 5.65 was calculated with respect to exposure to a specific risk factor. This means that the probability of developing a certain disease is</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>A 30-year-old man, otherwise healthy, is scheduled to undergo laparoscopic cholecystectomy. Which of the following procedures should be performed beforehand to reduce the perioperative risk:</t>
+          <t>A 30-year-old man, otherwise healthy, is scheduled to undergo laparoscopic cholecystectomy. Which of the following procedures should be performed beforehand to reduce the perioperative risk</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>A 32-year-old woman presents to the Emergency Department with palpitations. Her past medical history is unremarkable. On physical examination: GCS 15/15, SpO2 99% on room air, RR 29/minute, BP 110/65 mmHg, HR 180 bpm. The ECG shows the following tracing: paroxysmal supraventricular tachycardia due to nodal reentry. In light of the ECG findings and vital signs, which of the following is the most appropriate therapeutic intervention?</t>
+          <t>A 32-year-old woman presents to the Emergency Department with palpitations. Her past medical history is unremarkable. On physical examination: GCS 15/15, SpO2 99% on room air, RR 29/minute, BP 110/65 mmHg, HR 180 bpm. The ECG shows the following tracing: paroxysmal supraventricular tachycardia due to AV nodal reentry. In light of the ECG findings and vital signs, which of the following is the most appropriate therapeutic intervention?</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8328,6 +8328,31 @@
           <t>A 78-year-old woman is to undergo orthopedic surgery for reduction of a distal tibial fracture. The anesthesiologist decides to perform a popliteal sciatic nerve block with 15 mL of 0.5% bupivacaine and a femoral nerve block with 12 mL of 0.5% bupivacaine. Due to the temporary unavailability of an ultrasound device, the blocks are performed using a nerve stimulator. When the patient develops psychomotor agitation, 1 mg of Midazolam is administered. Subsequently, the patient reports a metallic taste and then develops a seizure. Based on the clinical suspicion, in addition to ensuring adequate airway management, it is indicated to proceed with:</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Intravenous administration of 20% lipid emulsion</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Administration of 100 mL of 3% hypertonic saline for suspected intracranial hypertension</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Continuous infusion of dexmedetomidine</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Administration of levetiracetam</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Administration of phenobarbital</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>A</t>
@@ -8358,7 +8383,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Proprioceptive rehabilitation aims at:</t>
+          <t>Proprioceptive rehabilitation aims at</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Medical Genetics; Oncology</t>
+          <t>Oncology; Medical Genetics</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ophthalmology; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Ophthalmology</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>General Surgery; Oncology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Endocrinology; Medical Genetics</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Gastroenterology; General Surgery</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Endocrinology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pediatrics; Infectious Diseases</t>
+          <t>Infectious Diseases; Pediatrics</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; Pharmacology and Toxicology</t>
+          <t>Pharmacology and Toxicology; Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Endocrinology; Oncology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Psychiatry; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Psychiatry</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Gastroenterology; Pharmacology and Toxicology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Anesthesia and Intensive Care</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Pharmacology and Toxicology</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Oncology; Hematology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Psychiatry</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics; General Surgery</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Neurology and Neurosurgery</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Medical Genetics; Pediatrics</t>
+          <t>Pediatrics; Infectious Diseases</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Forensic Medicine</t>
+          <t>Hygiene, Epidemiology and Statistics; Forensic Medicine</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Forensic Medicine; Pediatrics</t>
+          <t>Forensic Medicine</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Immunology and Rheumatology</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Urology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Pharmacology and Toxicology</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Pulmonology and Thoracic Surgery</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
@@ -4482,7 +4482,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endoscopic image </t>
+          <t>Endoscopic image</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2023_EN.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -473,15 +473,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Image Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Image Path</t>
         </is>
@@ -544,6 +549,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -602,6 +612,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -660,6 +675,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -718,6 +738,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,6 +801,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -834,6 +864,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +927,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -950,6 +990,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1008,6 +1053,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1066,6 +1116,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1124,6 +1179,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1182,6 +1242,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1240,6 +1305,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1298,6 +1368,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1356,6 +1431,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1414,6 +1494,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1469,7 +1554,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1530,6 +1620,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1588,6 +1683,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1648,10 +1748,15 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>images/2023/ssm2023460.png</t>
         </is>
@@ -1716,10 +1821,15 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>images/2023/ssm2023461.png</t>
         </is>
@@ -1782,6 +1892,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1840,6 +1955,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1898,6 +2018,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1956,6 +2081,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2014,6 +2144,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2072,6 +2207,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2130,6 +2270,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2188,6 +2333,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2246,6 +2396,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2304,6 +2459,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2362,6 +2522,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2420,6 +2585,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2478,6 +2648,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2536,6 +2711,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2594,6 +2774,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2652,6 +2837,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2710,6 +2900,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2768,6 +2963,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2826,6 +3026,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2884,6 +3089,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2942,6 +3152,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3000,6 +3215,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3058,6 +3278,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3116,6 +3341,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3174,6 +3404,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3232,6 +3467,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3290,6 +3530,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3348,6 +3593,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3408,10 +3658,15 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>images/2023/ssm2023490.png</t>
         </is>
@@ -3476,10 +3731,15 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>images/2023/ssm2023491.png</t>
         </is>
@@ -3544,10 +3804,15 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>Peripheral blood smear</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>images/2023/ssm2023492.png</t>
         </is>
@@ -3610,6 +3875,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3668,6 +3938,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3726,6 +4001,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3784,6 +4064,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3842,6 +4127,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3900,6 +4190,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3958,6 +4253,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4016,6 +4316,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4074,6 +4379,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4132,6 +4442,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4190,6 +4505,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4248,6 +4568,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4306,6 +4631,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4364,6 +4694,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4422,6 +4757,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4482,10 +4822,15 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
           <t>Endoscopic image</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>images/2023/ssm2023508.png</t>
         </is>
@@ -4548,6 +4893,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4606,6 +4956,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4664,6 +5019,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4722,6 +5082,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4780,6 +5145,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4838,6 +5208,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4896,6 +5271,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4954,6 +5334,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5012,6 +5397,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5070,6 +5460,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5130,10 +5525,15 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>images/2023/ssm2023519.png</t>
         </is>
@@ -5196,6 +5596,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5254,6 +5659,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5312,6 +5722,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5370,6 +5785,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5428,6 +5848,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5486,6 +5911,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5544,6 +5974,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5602,6 +6037,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5660,6 +6100,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5718,6 +6163,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5776,6 +6226,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5834,6 +6289,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5892,6 +6352,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5950,6 +6415,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6008,6 +6478,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6066,6 +6541,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6124,6 +6604,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6182,6 +6667,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6240,6 +6730,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6298,6 +6793,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6356,6 +6856,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6414,6 +6919,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6472,6 +6982,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6530,6 +7045,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6588,6 +7108,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6646,6 +7171,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6706,10 +7236,15 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>images/2023/ssm2023546.png</t>
         </is>
@@ -6772,6 +7307,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6832,10 +7372,15 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t>images/2023/ssm2023548.png</t>
         </is>
@@ -6900,10 +7445,15 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t>images/2023/ssm2023549.png</t>
         </is>
@@ -6966,6 +7516,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7024,6 +7579,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7082,6 +7642,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7140,6 +7705,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7198,6 +7768,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7256,6 +7831,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7314,6 +7894,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7372,6 +7957,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7430,6 +8020,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7488,6 +8083,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7546,6 +8146,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7604,6 +8209,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7662,6 +8272,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7720,6 +8335,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7778,6 +8398,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7836,6 +8461,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7894,6 +8524,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7952,6 +8587,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8010,6 +8650,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8068,6 +8713,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8126,6 +8776,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8184,6 +8839,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8244,10 +8904,15 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
+      <c r="O133" t="inlineStr">
         <is>
           <t>images/2023/ssm2023572.png</t>
         </is>
@@ -8310,6 +8975,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8368,6 +9038,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8426,6 +9101,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8484,6 +9164,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8542,6 +9227,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8600,6 +9290,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8658,6 +9353,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8714,6 +9414,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>case-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
